--- a/Archivos/Template/Template_HRC_olimpica.xlsx
+++ b/Archivos/Template/Template_HRC_olimpica.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Remittance" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -16,8 +17,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="4">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+  </numFmts>
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,6 +36,21 @@
     </font>
     <font>
       <color rgb="00000000"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -79,7 +97,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
@@ -102,6 +120,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2192,4 +2238,5490 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN66"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="35.5546875" customWidth="1" min="1" max="1"/>
+    <col width="22.33203125" customWidth="1" min="2" max="2"/>
+    <col width="30.77734375" customWidth="1" min="3" max="3"/>
+    <col width="15.109375" customWidth="1" min="4" max="4"/>
+    <col width="10.33203125" customWidth="1" min="5" max="5"/>
+    <col width="18.6640625" customWidth="1" min="6" max="6"/>
+    <col width="28.44140625" customWidth="1" min="7" max="7"/>
+    <col width="11.33203125" customWidth="1" min="8" max="8"/>
+    <col width="10.88671875" customWidth="1" min="9" max="9"/>
+    <col width="14.21875" customWidth="1" min="10" max="10"/>
+    <col width="13.109375" customWidth="1" min="11" max="11"/>
+    <col width="10.77734375" customWidth="1" min="12" max="12"/>
+    <col width="18.33203125" customWidth="1" min="13" max="13"/>
+    <col width="15.33203125" customWidth="1" min="14" max="14"/>
+    <col width="12.5546875" customWidth="1" min="15" max="15"/>
+    <col width="7.109375" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="9.77734375" customWidth="1" min="18" max="18"/>
+    <col width="10.6640625" customWidth="1" min="19" max="19"/>
+    <col width="7.33203125" customWidth="1" min="20" max="20"/>
+    <col width="7.33203125" customWidth="1" min="22" max="22"/>
+    <col width="7.5546875" customWidth="1" min="23" max="23"/>
+    <col width="7.6640625" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="10.77734375" customWidth="1" min="26" max="26"/>
+    <col width="17.6640625" customWidth="1" min="27" max="27"/>
+    <col width="13.109375" customWidth="1" min="28" max="28"/>
+    <col width="13.44140625" customWidth="1" min="29" max="29"/>
+    <col width="6.109375" customWidth="1" min="30" max="30"/>
+    <col width="28.77734375" customWidth="1" min="31" max="31"/>
+    <col width="19.109375" customWidth="1" min="32" max="32"/>
+    <col width="18.44140625" customWidth="1" min="33" max="33"/>
+    <col width="25.21875" customWidth="1" min="34" max="34"/>
+    <col width="15.6640625" customWidth="1" min="35" max="35"/>
+    <col width="28.88671875" customWidth="1" min="36" max="36"/>
+    <col width="15.6640625" customWidth="1" min="37" max="37"/>
+    <col width="28.88671875" customWidth="1" min="38" max="38"/>
+    <col width="15.6640625" customWidth="1" min="39" max="39"/>
+    <col width="28.88671875" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="12" t="n"/>
+    </row>
+    <row r="2" ht="14.4" customHeight="1">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>Informe de Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="14" t="n"/>
+    </row>
+    <row r="4" ht="14.4" customHeight="1">
+      <c r="A4" s="15" t="inlineStr">
+        <is>
+          <t>Información General</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="28.8" customHeight="1">
+      <c r="A5" s="16" t="inlineStr">
+        <is>
+          <t>Socio Comercial: Supertiendas y Droguerias Olimpicas S.A.</t>
+        </is>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>No. Aviso.: 00590139</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>Fecha Aviso: 29-08-2025</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="inlineStr">
+        <is>
+          <t>Socio Comercial : Unilever Andina S.A.</t>
+        </is>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Per. Facturación: </t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="inlineStr">
+        <is>
+          <t>Beneficiario 2 : Unilever Andina S.A.</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="n"/>
+    </row>
+    <row r="8" ht="14.4" customHeight="1">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>Información de Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
+        <is>
+          <t>Beneficiario : -- -- --</t>
+        </is>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>Nit : 7702006999328</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>Cód. Interno Proveedor: 0000100576</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Identificación Beneficiario: EAN</t>
+        </is>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Sucursal: Bogota</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>Orden de Pago: PK003702736775</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Medio de Pago: TEF</t>
+        </is>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>Nro. Cheque: 3702736775</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fecha Tasa Cambio: </t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ciudad de Pago: </t>
+        </is>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Fecha Pago: 29-08-2025</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moneda Pago: </t>
+        </is>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tasa Cambio: 0.000000</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moneda Facturación: </t>
+        </is>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Canal de Pago: 6</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="n"/>
+    </row>
+    <row r="15" ht="14.4" customHeight="1">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Información Bancaria</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Receptor: </t>
+        </is>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banco Emisor: </t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="n"/>
+      <c r="D16" s="17" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cód. Sucursal Receptor: </t>
+        </is>
+      </c>
+      <c r="B17" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cód. Sucursal Emisor: </t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. Cuenta Receptor: </t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">No. Cuenta Emisor: </t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo Cuenta Receptor: </t>
+        </is>
+      </c>
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tipo Cuenta Emisor: </t>
+        </is>
+      </c>
+      <c r="N19" s="18" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Titular Cuenta Receptor: </t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="n"/>
+      <c r="N20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="16" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="n"/>
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="n"/>
+      <c r="N22" s="18" t="n"/>
+    </row>
+    <row r="23" ht="12.6" customHeight="1">
+      <c r="A23" s="17" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="n"/>
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="n"/>
+    </row>
+    <row r="25" ht="60" customHeight="1">
+      <c r="A25" s="19" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
+          <t>COD DOC</t>
+        </is>
+      </c>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>DOC</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>No. Interno</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>No. Doc</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="inlineStr">
+        <is>
+          <t>Fecha Doc</t>
+        </is>
+      </c>
+      <c r="F26" s="20" t="inlineStr">
+        <is>
+          <t>Cod Ean Sitio Entrega</t>
+        </is>
+      </c>
+      <c r="G26" s="20" t="inlineStr">
+        <is>
+          <t>Lugar Entrega</t>
+        </is>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Pedido</t>
+        </is>
+      </c>
+      <c r="I26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Factura</t>
+        </is>
+      </c>
+      <c r="J26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Avis Recibo</t>
+        </is>
+      </c>
+      <c r="K26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Avis Devol</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Dossier</t>
+        </is>
+      </c>
+      <c r="M26" s="20" t="inlineStr">
+        <is>
+          <t>Ref. Numero de Folio</t>
+        </is>
+      </c>
+      <c r="N26" s="20" t="inlineStr">
+        <is>
+          <t>Total a Pagar</t>
+        </is>
+      </c>
+      <c r="O26" s="20" t="inlineStr">
+        <is>
+          <t>Vlr Ant. Ajuste</t>
+        </is>
+      </c>
+      <c r="P26" s="20" t="inlineStr">
+        <is>
+          <t>Ajustes</t>
+        </is>
+      </c>
+      <c r="Q26" s="20" t="inlineStr">
+        <is>
+          <t>Iva</t>
+        </is>
+      </c>
+      <c r="R26" s="20" t="inlineStr">
+        <is>
+          <t>Impuestos</t>
+        </is>
+      </c>
+      <c r="S26" s="20" t="inlineStr">
+        <is>
+          <t>Descuentos</t>
+        </is>
+      </c>
+      <c r="T26" s="20" t="inlineStr">
+        <is>
+          <t>Vlr Hort</t>
+        </is>
+      </c>
+      <c r="U26" s="20" t="inlineStr">
+        <is>
+          <t>Valor Doc</t>
+        </is>
+      </c>
+      <c r="V26" s="20" t="inlineStr">
+        <is>
+          <t>Rete fte</t>
+        </is>
+      </c>
+      <c r="W26" s="20" t="inlineStr">
+        <is>
+          <t>Rete Iva</t>
+        </is>
+      </c>
+      <c r="X26" s="20" t="inlineStr">
+        <is>
+          <t>Rete Ica</t>
+        </is>
+      </c>
+      <c r="Y26" s="20" t="inlineStr">
+        <is>
+          <t>Rte. CREE</t>
+        </is>
+      </c>
+      <c r="Z26" s="20" t="inlineStr">
+        <is>
+          <t>Cod Ajustes</t>
+        </is>
+      </c>
+      <c r="AA26" s="20" t="inlineStr">
+        <is>
+          <t>Descripcion Ajustes</t>
+        </is>
+      </c>
+      <c r="AB26" s="20" t="inlineStr">
+        <is>
+          <t>Valor Ajustado</t>
+        </is>
+      </c>
+      <c r="AC26" s="20" t="inlineStr">
+        <is>
+          <t>Observaciones</t>
+        </is>
+      </c>
+      <c r="AD26" s="20" t="inlineStr">
+        <is>
+          <t>No Lin</t>
+        </is>
+      </c>
+      <c r="AE26" s="20" t="inlineStr">
+        <is>
+          <t>Código de identificación del Item</t>
+        </is>
+      </c>
+      <c r="AF26" s="20" t="inlineStr">
+        <is>
+          <t>Tipo de Identificación</t>
+        </is>
+      </c>
+      <c r="AG26" s="20" t="inlineStr">
+        <is>
+          <t>Descripción del Item</t>
+        </is>
+      </c>
+      <c r="AH26" s="20" t="inlineStr">
+        <is>
+          <t>Precio Neto Unitario del Item</t>
+        </is>
+      </c>
+      <c r="AI26" s="20" t="inlineStr">
+        <is>
+          <t>Razón del Ajuste1</t>
+        </is>
+      </c>
+      <c r="AJ26" s="20" t="inlineStr">
+        <is>
+          <t>Cantidad del Item para el Ajuste1</t>
+        </is>
+      </c>
+      <c r="AK26" s="20" t="inlineStr">
+        <is>
+          <t>Razón del Ajuste2</t>
+        </is>
+      </c>
+      <c r="AL26" s="20" t="inlineStr">
+        <is>
+          <t>Cantidad del Item para el Ajuste2</t>
+        </is>
+      </c>
+      <c r="AM26" s="20" t="inlineStr">
+        <is>
+          <t>Razón del Ajuste3</t>
+        </is>
+      </c>
+      <c r="AN26" s="20" t="inlineStr">
+        <is>
+          <t>Cantidad del Item para el Ajuste3</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>'5133526811</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249244001</t>
+        </is>
+      </c>
+      <c r="E27" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009608</t>
+        </is>
+      </c>
+      <c r="G27" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 960 Cross-Docking</t>
+        </is>
+      </c>
+      <c r="H27" s="16" t="inlineStr">
+        <is>
+          <t>'4632109353</t>
+        </is>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J27" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K27" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L27" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M27" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N27" s="16" t="n">
+        <v>31277975</v>
+      </c>
+      <c r="O27" s="16" t="n">
+        <v>27002606</v>
+      </c>
+      <c r="P27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="16" t="n">
+        <v>4275369</v>
+      </c>
+      <c r="R27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="16" t="n"/>
+      <c r="AA27" s="16" t="n"/>
+      <c r="AB27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" s="16" t="n"/>
+      <c r="AD27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" s="16" t="n"/>
+      <c r="AF27" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG27" s="16" t="n"/>
+      <c r="AH27" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI27" s="16" t="n"/>
+      <c r="AJ27" s="16" t="n"/>
+      <c r="AK27" s="16" t="n"/>
+      <c r="AL27" s="16" t="n"/>
+      <c r="AM27" s="16" t="n"/>
+      <c r="AN27" s="16" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>'5133559019</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249258001</t>
+        </is>
+      </c>
+      <c r="E28" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009608</t>
+        </is>
+      </c>
+      <c r="G28" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 960 Cross-Docking</t>
+        </is>
+      </c>
+      <c r="H28" s="16" t="inlineStr">
+        <is>
+          <t>'4632109351</t>
+        </is>
+      </c>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J28" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K28" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L28" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M28" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N28" s="16" t="n">
+        <v>1102345</v>
+      </c>
+      <c r="O28" s="16" t="n">
+        <v>926340</v>
+      </c>
+      <c r="P28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="16" t="n">
+        <v>176005</v>
+      </c>
+      <c r="R28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="16" t="n"/>
+      <c r="AA28" s="16" t="n"/>
+      <c r="AB28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="16" t="n"/>
+      <c r="AD28" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="16" t="n"/>
+      <c r="AF28" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG28" s="16" t="n"/>
+      <c r="AH28" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI28" s="16" t="n"/>
+      <c r="AJ28" s="16" t="n"/>
+      <c r="AK28" s="16" t="n"/>
+      <c r="AL28" s="16" t="n"/>
+      <c r="AM28" s="16" t="n"/>
+      <c r="AN28" s="16" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>'5132904345</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249400002</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F29" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G29" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H29" s="16" t="inlineStr">
+        <is>
+          <t>'4632027137</t>
+        </is>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J29" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K29" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L29" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M29" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N29" s="16" t="n">
+        <v>27692682</v>
+      </c>
+      <c r="O29" s="16" t="n">
+        <v>23902286</v>
+      </c>
+      <c r="P29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="16" t="n">
+        <v>3790396</v>
+      </c>
+      <c r="R29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="16" t="n"/>
+      <c r="AA29" s="16" t="n"/>
+      <c r="AB29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="16" t="n"/>
+      <c r="AD29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="16" t="n"/>
+      <c r="AF29" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG29" s="16" t="n"/>
+      <c r="AH29" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI29" s="16" t="n"/>
+      <c r="AJ29" s="16" t="n"/>
+      <c r="AK29" s="16" t="n"/>
+      <c r="AL29" s="16" t="n"/>
+      <c r="AM29" s="16" t="n"/>
+      <c r="AN29" s="16" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B30" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>'5133490119</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249405001</t>
+        </is>
+      </c>
+      <c r="E30" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G30" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H30" s="16" t="inlineStr">
+        <is>
+          <t>'4632100695</t>
+        </is>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J30" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K30" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L30" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M30" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N30" s="16" t="n">
+        <v>4992313</v>
+      </c>
+      <c r="O30" s="16" t="n">
+        <v>4309915</v>
+      </c>
+      <c r="P30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="16" t="n">
+        <v>682398</v>
+      </c>
+      <c r="R30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="16" t="n"/>
+      <c r="AA30" s="16" t="n"/>
+      <c r="AB30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="16" t="n"/>
+      <c r="AD30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="16" t="n"/>
+      <c r="AF30" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG30" s="16" t="n"/>
+      <c r="AH30" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI30" s="16" t="n"/>
+      <c r="AJ30" s="16" t="n"/>
+      <c r="AK30" s="16" t="n"/>
+      <c r="AL30" s="16" t="n"/>
+      <c r="AM30" s="16" t="n"/>
+      <c r="AN30" s="16" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>'5133108726</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249557001</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009608</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 960 Cross-Docking</t>
+        </is>
+      </c>
+      <c r="H31" s="16" t="inlineStr">
+        <is>
+          <t>'4632109349</t>
+        </is>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J31" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K31" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L31" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M31" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N31" s="16" t="n">
+        <v>20100423</v>
+      </c>
+      <c r="O31" s="16" t="n">
+        <v>16891112</v>
+      </c>
+      <c r="P31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="16" t="n">
+        <v>3209311</v>
+      </c>
+      <c r="R31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="16" t="n"/>
+      <c r="AA31" s="16" t="n"/>
+      <c r="AB31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="16" t="n"/>
+      <c r="AD31" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="16" t="n"/>
+      <c r="AF31" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG31" s="16" t="n"/>
+      <c r="AH31" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI31" s="16" t="n"/>
+      <c r="AJ31" s="16" t="n"/>
+      <c r="AK31" s="16" t="n"/>
+      <c r="AL31" s="16" t="n"/>
+      <c r="AM31" s="16" t="n"/>
+      <c r="AN31" s="16" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B32" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="inlineStr">
+        <is>
+          <t>'5133559878</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249558002</t>
+        </is>
+      </c>
+      <c r="E32" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F32" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009608</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 960 Cross-Docking</t>
+        </is>
+      </c>
+      <c r="H32" s="16" t="inlineStr">
+        <is>
+          <t>'4632109354</t>
+        </is>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J32" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K32" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L32" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M32" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N32" s="16" t="n">
+        <v>72307698</v>
+      </c>
+      <c r="O32" s="16" t="n">
+        <v>60762772</v>
+      </c>
+      <c r="P32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="16" t="n">
+        <v>11544926</v>
+      </c>
+      <c r="R32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="16" t="n"/>
+      <c r="AA32" s="16" t="n"/>
+      <c r="AB32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="16" t="n"/>
+      <c r="AD32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="16" t="n"/>
+      <c r="AF32" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG32" s="16" t="n"/>
+      <c r="AH32" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI32" s="16" t="n"/>
+      <c r="AJ32" s="16" t="n"/>
+      <c r="AK32" s="16" t="n"/>
+      <c r="AL32" s="16" t="n"/>
+      <c r="AM32" s="16" t="n"/>
+      <c r="AN32" s="16" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>'5133510025</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249559002</t>
+        </is>
+      </c>
+      <c r="E33" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G33" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H33" s="16" t="inlineStr">
+        <is>
+          <t>'4632066563</t>
+        </is>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J33" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K33" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L33" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M33" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N33" s="16" t="n">
+        <v>94379986</v>
+      </c>
+      <c r="O33" s="16" t="n">
+        <v>79310913</v>
+      </c>
+      <c r="P33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="16" t="n">
+        <v>15069073</v>
+      </c>
+      <c r="R33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="16" t="n"/>
+      <c r="AA33" s="16" t="n"/>
+      <c r="AB33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="16" t="n"/>
+      <c r="AD33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="16" t="n"/>
+      <c r="AF33" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG33" s="16" t="n"/>
+      <c r="AH33" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI33" s="16" t="n"/>
+      <c r="AJ33" s="16" t="n"/>
+      <c r="AK33" s="16" t="n"/>
+      <c r="AL33" s="16" t="n"/>
+      <c r="AM33" s="16" t="n"/>
+      <c r="AN33" s="16" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B34" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C34" s="16" t="inlineStr">
+        <is>
+          <t>'5133550902</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249560001</t>
+        </is>
+      </c>
+      <c r="E34" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F34" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G34" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H34" s="16" t="inlineStr">
+        <is>
+          <t>'4632027135</t>
+        </is>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J34" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K34" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L34" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M34" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N34" s="16" t="n">
+        <v>2263380</v>
+      </c>
+      <c r="O34" s="16" t="n">
+        <v>1902000</v>
+      </c>
+      <c r="P34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="16" t="n">
+        <v>361380</v>
+      </c>
+      <c r="R34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="16" t="n"/>
+      <c r="AA34" s="16" t="n"/>
+      <c r="AB34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="16" t="n"/>
+      <c r="AD34" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="16" t="n"/>
+      <c r="AF34" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG34" s="16" t="n"/>
+      <c r="AH34" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI34" s="16" t="n"/>
+      <c r="AJ34" s="16" t="n"/>
+      <c r="AK34" s="16" t="n"/>
+      <c r="AL34" s="16" t="n"/>
+      <c r="AM34" s="16" t="n"/>
+      <c r="AN34" s="16" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B35" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>'5133474648</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249561001</t>
+        </is>
+      </c>
+      <c r="E35" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G35" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H35" s="16" t="inlineStr">
+        <is>
+          <t>'4632027134</t>
+        </is>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J35" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K35" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L35" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M35" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N35" s="16" t="n">
+        <v>79954317</v>
+      </c>
+      <c r="O35" s="16" t="n">
+        <v>67188501</v>
+      </c>
+      <c r="P35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="16" t="n">
+        <v>12765816</v>
+      </c>
+      <c r="R35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="16" t="n"/>
+      <c r="AA35" s="16" t="n"/>
+      <c r="AB35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" s="16" t="n"/>
+      <c r="AD35" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="16" t="n"/>
+      <c r="AF35" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG35" s="16" t="n"/>
+      <c r="AH35" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI35" s="16" t="n"/>
+      <c r="AJ35" s="16" t="n"/>
+      <c r="AK35" s="16" t="n"/>
+      <c r="AL35" s="16" t="n"/>
+      <c r="AM35" s="16" t="n"/>
+      <c r="AN35" s="16" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B36" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>'5133513191</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249562001</t>
+        </is>
+      </c>
+      <c r="E36" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F36" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G36" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H36" s="16" t="inlineStr">
+        <is>
+          <t>'4632100692</t>
+        </is>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J36" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K36" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L36" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M36" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N36" s="16" t="n">
+        <v>19480076</v>
+      </c>
+      <c r="O36" s="16" t="n">
+        <v>16369812</v>
+      </c>
+      <c r="P36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="16" t="n">
+        <v>3110264</v>
+      </c>
+      <c r="R36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="16" t="n"/>
+      <c r="AA36" s="16" t="n"/>
+      <c r="AB36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" s="16" t="n"/>
+      <c r="AD36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" s="16" t="n"/>
+      <c r="AF36" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG36" s="16" t="n"/>
+      <c r="AH36" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI36" s="16" t="n"/>
+      <c r="AJ36" s="16" t="n"/>
+      <c r="AK36" s="16" t="n"/>
+      <c r="AL36" s="16" t="n"/>
+      <c r="AM36" s="16" t="n"/>
+      <c r="AN36" s="16" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B37" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>'5133423397</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249563002</t>
+        </is>
+      </c>
+      <c r="E37" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F37" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G37" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H37" s="16" t="inlineStr">
+        <is>
+          <t>'4632027134</t>
+        </is>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J37" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K37" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L37" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M37" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="n">
+        <v>122200697</v>
+      </c>
+      <c r="O37" s="16" t="n">
+        <v>102689662</v>
+      </c>
+      <c r="P37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="16" t="n">
+        <v>19511035</v>
+      </c>
+      <c r="R37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="16" t="n"/>
+      <c r="AA37" s="16" t="n"/>
+      <c r="AB37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" s="16" t="n"/>
+      <c r="AD37" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" s="16" t="n"/>
+      <c r="AF37" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG37" s="16" t="n"/>
+      <c r="AH37" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI37" s="16" t="n"/>
+      <c r="AJ37" s="16" t="n"/>
+      <c r="AK37" s="16" t="n"/>
+      <c r="AL37" s="16" t="n"/>
+      <c r="AM37" s="16" t="n"/>
+      <c r="AN37" s="16" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="inlineStr">
+        <is>
+          <t>'5133544136</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249564001</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F38" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G38" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H38" s="16" t="inlineStr">
+        <is>
+          <t>'4632100692</t>
+        </is>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J38" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K38" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L38" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M38" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N38" s="16" t="n">
+        <v>7344450</v>
+      </c>
+      <c r="O38" s="16" t="n">
+        <v>6171807</v>
+      </c>
+      <c r="P38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="16" t="n">
+        <v>1172643</v>
+      </c>
+      <c r="R38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="16" t="n"/>
+      <c r="AA38" s="16" t="n"/>
+      <c r="AB38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" s="16" t="n"/>
+      <c r="AD38" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" s="16" t="n"/>
+      <c r="AF38" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG38" s="16" t="n"/>
+      <c r="AH38" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI38" s="16" t="n"/>
+      <c r="AJ38" s="16" t="n"/>
+      <c r="AK38" s="16" t="n"/>
+      <c r="AL38" s="16" t="n"/>
+      <c r="AM38" s="16" t="n"/>
+      <c r="AN38" s="16" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B39" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>'5133567944</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249565002</t>
+        </is>
+      </c>
+      <c r="E39" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F39" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G39" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>'4632027138</t>
+        </is>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J39" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K39" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L39" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M39" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N39" s="16" t="n">
+        <v>75077367</v>
+      </c>
+      <c r="O39" s="16" t="n">
+        <v>63090225</v>
+      </c>
+      <c r="P39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="16" t="n">
+        <v>11987142</v>
+      </c>
+      <c r="R39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="16" t="n"/>
+      <c r="AA39" s="16" t="n"/>
+      <c r="AB39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" s="16" t="n"/>
+      <c r="AD39" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" s="16" t="n"/>
+      <c r="AF39" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG39" s="16" t="n"/>
+      <c r="AH39" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI39" s="16" t="n"/>
+      <c r="AJ39" s="16" t="n"/>
+      <c r="AK39" s="16" t="n"/>
+      <c r="AL39" s="16" t="n"/>
+      <c r="AM39" s="16" t="n"/>
+      <c r="AN39" s="16" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B40" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>'5133446644</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249566001</t>
+        </is>
+      </c>
+      <c r="E40" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G40" s="16" t="inlineStr">
+        <is>
+          <t>'Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>'4632100696</t>
+        </is>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J40" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K40" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L40" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M40" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="n">
+        <v>15478421</v>
+      </c>
+      <c r="O40" s="16" t="n">
+        <v>13007077</v>
+      </c>
+      <c r="P40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="16" t="n">
+        <v>2471344</v>
+      </c>
+      <c r="R40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="16" t="n"/>
+      <c r="AA40" s="16" t="n"/>
+      <c r="AB40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" s="16" t="n"/>
+      <c r="AD40" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" s="16" t="n"/>
+      <c r="AF40" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG40" s="16" t="n"/>
+      <c r="AH40" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI40" s="16" t="n"/>
+      <c r="AJ40" s="16" t="n"/>
+      <c r="AK40" s="16" t="n"/>
+      <c r="AL40" s="16" t="n"/>
+      <c r="AM40" s="16" t="n"/>
+      <c r="AN40" s="16" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B41" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>'5132667367</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249894001</t>
+        </is>
+      </c>
+      <c r="E41" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F41" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G41" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H41" s="16" t="inlineStr">
+        <is>
+          <t>'4631938987</t>
+        </is>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J41" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K41" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L41" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M41" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N41" s="16" t="n">
+        <v>5509234</v>
+      </c>
+      <c r="O41" s="16" t="n">
+        <v>4756176</v>
+      </c>
+      <c r="P41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="16" t="n">
+        <v>753058</v>
+      </c>
+      <c r="R41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="16" t="n"/>
+      <c r="AA41" s="16" t="n"/>
+      <c r="AB41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC41" s="16" t="n"/>
+      <c r="AD41" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE41" s="16" t="n"/>
+      <c r="AF41" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG41" s="16" t="n"/>
+      <c r="AH41" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI41" s="16" t="n"/>
+      <c r="AJ41" s="16" t="n"/>
+      <c r="AK41" s="16" t="n"/>
+      <c r="AL41" s="16" t="n"/>
+      <c r="AM41" s="16" t="n"/>
+      <c r="AN41" s="16" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B42" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>'5133433219</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249897001</t>
+        </is>
+      </c>
+      <c r="E42" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F42" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G42" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H42" s="16" t="inlineStr">
+        <is>
+          <t>'4632003302</t>
+        </is>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J42" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K42" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L42" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M42" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N42" s="16" t="n">
+        <v>11607265</v>
+      </c>
+      <c r="O42" s="16" t="n">
+        <v>10020669</v>
+      </c>
+      <c r="P42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="16" t="n">
+        <v>1586596</v>
+      </c>
+      <c r="R42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="16" t="n"/>
+      <c r="AA42" s="16" t="n"/>
+      <c r="AB42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="16" t="n"/>
+      <c r="AD42" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE42" s="16" t="n"/>
+      <c r="AF42" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG42" s="16" t="n"/>
+      <c r="AH42" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI42" s="16" t="n"/>
+      <c r="AJ42" s="16" t="n"/>
+      <c r="AK42" s="16" t="n"/>
+      <c r="AL42" s="16" t="n"/>
+      <c r="AM42" s="16" t="n"/>
+      <c r="AN42" s="16" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B43" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>'5133015257</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249898001</t>
+        </is>
+      </c>
+      <c r="E43" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F43" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G43" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H43" s="16" t="inlineStr">
+        <is>
+          <t>'4631865203</t>
+        </is>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J43" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K43" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L43" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M43" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="n">
+        <v>3747972</v>
+      </c>
+      <c r="O43" s="16" t="n">
+        <v>3149557</v>
+      </c>
+      <c r="P43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="16" t="n">
+        <v>598415</v>
+      </c>
+      <c r="R43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="16" t="n"/>
+      <c r="AA43" s="16" t="n"/>
+      <c r="AB43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" s="16" t="n"/>
+      <c r="AD43" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" s="16" t="n"/>
+      <c r="AF43" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG43" s="16" t="n"/>
+      <c r="AH43" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI43" s="16" t="n"/>
+      <c r="AJ43" s="16" t="n"/>
+      <c r="AK43" s="16" t="n"/>
+      <c r="AL43" s="16" t="n"/>
+      <c r="AM43" s="16" t="n"/>
+      <c r="AN43" s="16" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B44" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>'5133460746</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249901001</t>
+        </is>
+      </c>
+      <c r="E44" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F44" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G44" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>'4631938985</t>
+        </is>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J44" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K44" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L44" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M44" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="n">
+        <v>1322814</v>
+      </c>
+      <c r="O44" s="16" t="n">
+        <v>1111608</v>
+      </c>
+      <c r="P44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="16" t="n">
+        <v>211206</v>
+      </c>
+      <c r="R44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="16" t="n"/>
+      <c r="AA44" s="16" t="n"/>
+      <c r="AB44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="16" t="n"/>
+      <c r="AD44" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" s="16" t="n"/>
+      <c r="AF44" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG44" s="16" t="n"/>
+      <c r="AH44" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI44" s="16" t="n"/>
+      <c r="AJ44" s="16" t="n"/>
+      <c r="AK44" s="16" t="n"/>
+      <c r="AL44" s="16" t="n"/>
+      <c r="AM44" s="16" t="n"/>
+      <c r="AN44" s="16" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B45" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>'5133508297</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249972001</t>
+        </is>
+      </c>
+      <c r="E45" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F45" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G45" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H45" s="16" t="inlineStr">
+        <is>
+          <t>'4632066562</t>
+        </is>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J45" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K45" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L45" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M45" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N45" s="16" t="n">
+        <v>125839982</v>
+      </c>
+      <c r="O45" s="16" t="n">
+        <v>105747884</v>
+      </c>
+      <c r="P45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="16" t="n">
+        <v>20092098</v>
+      </c>
+      <c r="R45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="16" t="n"/>
+      <c r="AA45" s="16" t="n"/>
+      <c r="AB45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="16" t="n"/>
+      <c r="AD45" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" s="16" t="n"/>
+      <c r="AF45" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG45" s="16" t="n"/>
+      <c r="AH45" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI45" s="16" t="n"/>
+      <c r="AJ45" s="16" t="n"/>
+      <c r="AK45" s="16" t="n"/>
+      <c r="AL45" s="16" t="n"/>
+      <c r="AM45" s="16" t="n"/>
+      <c r="AN45" s="16" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B46" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>'5132449468</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249973001</t>
+        </is>
+      </c>
+      <c r="E46" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F46" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G46" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>'4632003298</t>
+        </is>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J46" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L46" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M46" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N46" s="16" t="n">
+        <v>28730082</v>
+      </c>
+      <c r="O46" s="16" t="n">
+        <v>24142926</v>
+      </c>
+      <c r="P46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="16" t="n">
+        <v>4587156</v>
+      </c>
+      <c r="R46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="16" t="n"/>
+      <c r="AA46" s="16" t="n"/>
+      <c r="AB46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="16" t="n"/>
+      <c r="AD46" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" s="16" t="n"/>
+      <c r="AF46" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG46" s="16" t="n"/>
+      <c r="AH46" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI46" s="16" t="n"/>
+      <c r="AJ46" s="16" t="n"/>
+      <c r="AK46" s="16" t="n"/>
+      <c r="AL46" s="16" t="n"/>
+      <c r="AM46" s="16" t="n"/>
+      <c r="AN46" s="16" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B47" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>'5133492585</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249974001</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F47" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G47" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H47" s="16" t="inlineStr">
+        <is>
+          <t>'4632003299</t>
+        </is>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J47" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L47" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M47" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="n">
+        <v>3055563</v>
+      </c>
+      <c r="O47" s="16" t="n">
+        <v>2567700</v>
+      </c>
+      <c r="P47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="16" t="n">
+        <v>487863</v>
+      </c>
+      <c r="R47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="16" t="n"/>
+      <c r="AA47" s="16" t="n"/>
+      <c r="AB47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" s="16" t="n"/>
+      <c r="AD47" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" s="16" t="n"/>
+      <c r="AF47" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG47" s="16" t="n"/>
+      <c r="AH47" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI47" s="16" t="n"/>
+      <c r="AJ47" s="16" t="n"/>
+      <c r="AK47" s="16" t="n"/>
+      <c r="AL47" s="16" t="n"/>
+      <c r="AM47" s="16" t="n"/>
+      <c r="AN47" s="16" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B48" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>'5132740196</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249975001</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F48" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H48" s="16" t="inlineStr">
+        <is>
+          <t>'4632003298</t>
+        </is>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J48" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K48" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L48" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M48" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N48" s="16" t="n">
+        <v>198843616</v>
+      </c>
+      <c r="O48" s="16" t="n">
+        <v>167095476</v>
+      </c>
+      <c r="P48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="16" t="n">
+        <v>31748140</v>
+      </c>
+      <c r="R48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="16" t="n"/>
+      <c r="AA48" s="16" t="n"/>
+      <c r="AB48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" s="16" t="n"/>
+      <c r="AD48" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" s="16" t="n"/>
+      <c r="AF48" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG48" s="16" t="n"/>
+      <c r="AH48" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI48" s="16" t="n"/>
+      <c r="AJ48" s="16" t="n"/>
+      <c r="AK48" s="16" t="n"/>
+      <c r="AL48" s="16" t="n"/>
+      <c r="AM48" s="16" t="n"/>
+      <c r="AN48" s="16" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="inlineStr">
+        <is>
+          <t>'5133537183</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249976001</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F49" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H49" s="16" t="inlineStr">
+        <is>
+          <t>'4632003303</t>
+        </is>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J49" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K49" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L49" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M49" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N49" s="16" t="n">
+        <v>86264216</v>
+      </c>
+      <c r="O49" s="16" t="n">
+        <v>72490938</v>
+      </c>
+      <c r="P49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="16" t="n">
+        <v>13773278</v>
+      </c>
+      <c r="R49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="16" t="n"/>
+      <c r="AA49" s="16" t="n"/>
+      <c r="AB49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="16" t="n"/>
+      <c r="AD49" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" s="16" t="n"/>
+      <c r="AF49" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG49" s="16" t="n"/>
+      <c r="AH49" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI49" s="16" t="n"/>
+      <c r="AJ49" s="16" t="n"/>
+      <c r="AK49" s="16" t="n"/>
+      <c r="AL49" s="16" t="n"/>
+      <c r="AM49" s="16" t="n"/>
+      <c r="AN49" s="16" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B50" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>'5133500457</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250219001</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F50" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H50" s="16" t="inlineStr">
+        <is>
+          <t>'4632092530</t>
+        </is>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J50" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K50" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L50" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M50" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="n">
+        <v>62919991</v>
+      </c>
+      <c r="O50" s="16" t="n">
+        <v>52873942</v>
+      </c>
+      <c r="P50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="16" t="n">
+        <v>10046049</v>
+      </c>
+      <c r="R50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="16" t="n"/>
+      <c r="AA50" s="16" t="n"/>
+      <c r="AB50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="16" t="n"/>
+      <c r="AD50" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="16" t="n"/>
+      <c r="AF50" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG50" s="16" t="n"/>
+      <c r="AH50" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI50" s="16" t="n"/>
+      <c r="AJ50" s="16" t="n"/>
+      <c r="AK50" s="16" t="n"/>
+      <c r="AL50" s="16" t="n"/>
+      <c r="AM50" s="16" t="n"/>
+      <c r="AN50" s="16" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B51" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C51" s="16" t="inlineStr">
+        <is>
+          <t>'5133446704</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250222001</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F51" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H51" s="16" t="inlineStr">
+        <is>
+          <t>'4631938984</t>
+        </is>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J51" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K51" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L51" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M51" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="n">
+        <v>2602887</v>
+      </c>
+      <c r="O51" s="16" t="n">
+        <v>2187300</v>
+      </c>
+      <c r="P51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="16" t="n">
+        <v>415587</v>
+      </c>
+      <c r="R51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="16" t="n"/>
+      <c r="AA51" s="16" t="n"/>
+      <c r="AB51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="16" t="n"/>
+      <c r="AD51" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="16" t="n"/>
+      <c r="AF51" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG51" s="16" t="n"/>
+      <c r="AH51" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI51" s="16" t="n"/>
+      <c r="AJ51" s="16" t="n"/>
+      <c r="AK51" s="16" t="n"/>
+      <c r="AL51" s="16" t="n"/>
+      <c r="AM51" s="16" t="n"/>
+      <c r="AN51" s="16" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C52" s="16" t="inlineStr">
+        <is>
+          <t>'5133428310</t>
+        </is>
+      </c>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250223001</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F52" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H52" s="16" t="inlineStr">
+        <is>
+          <t>'4631938983</t>
+        </is>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J52" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K52" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L52" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M52" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N52" s="16" t="n">
+        <v>39567495</v>
+      </c>
+      <c r="O52" s="16" t="n">
+        <v>33249996</v>
+      </c>
+      <c r="P52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" s="16" t="n">
+        <v>6317499</v>
+      </c>
+      <c r="R52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="16" t="n"/>
+      <c r="AA52" s="16" t="n"/>
+      <c r="AB52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" s="16" t="n"/>
+      <c r="AD52" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="16" t="n"/>
+      <c r="AF52" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG52" s="16" t="n"/>
+      <c r="AH52" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI52" s="16" t="n"/>
+      <c r="AJ52" s="16" t="n"/>
+      <c r="AK52" s="16" t="n"/>
+      <c r="AL52" s="16" t="n"/>
+      <c r="AM52" s="16" t="n"/>
+      <c r="AN52" s="16" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C53" s="16" t="inlineStr">
+        <is>
+          <t>'5132789191</t>
+        </is>
+      </c>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250224001</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F53" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H53" s="16" t="inlineStr">
+        <is>
+          <t>'4631938983</t>
+        </is>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J53" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K53" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L53" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M53" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N53" s="16" t="n">
+        <v>10928542</v>
+      </c>
+      <c r="O53" s="16" t="n">
+        <v>9183648</v>
+      </c>
+      <c r="P53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="16" t="n">
+        <v>1744894</v>
+      </c>
+      <c r="R53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="16" t="n"/>
+      <c r="AA53" s="16" t="n"/>
+      <c r="AB53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="16" t="n"/>
+      <c r="AD53" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="16" t="n"/>
+      <c r="AF53" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG53" s="16" t="n"/>
+      <c r="AH53" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI53" s="16" t="n"/>
+      <c r="AJ53" s="16" t="n"/>
+      <c r="AK53" s="16" t="n"/>
+      <c r="AL53" s="16" t="n"/>
+      <c r="AM53" s="16" t="n"/>
+      <c r="AN53" s="16" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="n">
+        <v>380</v>
+      </c>
+      <c r="B54" s="16" t="inlineStr">
+        <is>
+          <t>Factura Comercial</t>
+        </is>
+      </c>
+      <c r="C54" s="16" t="inlineStr">
+        <is>
+          <t>'5133584850</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250225001</t>
+        </is>
+      </c>
+      <c r="E54" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F54" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>'Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H54" s="16" t="inlineStr">
+        <is>
+          <t>'4631938988</t>
+        </is>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J54" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K54" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L54" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M54" s="16" t="inlineStr">
+        <is>
+          <t>''</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="n">
+        <v>34995137</v>
+      </c>
+      <c r="O54" s="16" t="n">
+        <v>29407678</v>
+      </c>
+      <c r="P54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="16" t="n">
+        <v>5587459</v>
+      </c>
+      <c r="R54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="16" t="n"/>
+      <c r="AA54" s="16" t="n"/>
+      <c r="AB54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="16" t="n"/>
+      <c r="AD54" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="16" t="n"/>
+      <c r="AF54" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG54" s="16" t="n"/>
+      <c r="AH54" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI54" s="16" t="n"/>
+      <c r="AJ54" s="16" t="n"/>
+      <c r="AK54" s="16" t="n"/>
+      <c r="AL54" s="16" t="n"/>
+      <c r="AM54" s="16" t="n"/>
+      <c r="AN54" s="16" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B55" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C55" s="16" t="inlineStr">
+        <is>
+          <t>'5213419654</t>
+        </is>
+      </c>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>'4633807051001</t>
+        </is>
+      </c>
+      <c r="E55" s="21" t="n">
+        <v>45897</v>
+      </c>
+      <c r="F55" s="16" t="inlineStr">
+        <is>
+          <t>'7701008003132</t>
+        </is>
+      </c>
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>STO 313 CIENAGA DE ORO</t>
+        </is>
+      </c>
+      <c r="H55" s="16" t="inlineStr">
+        <is>
+          <t>'4633807051</t>
+        </is>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J55" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K55" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L55" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M55" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N55" s="16" t="n">
+        <v>-7083</v>
+      </c>
+      <c r="O55" s="16" t="n">
+        <v>-5952</v>
+      </c>
+      <c r="P55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="16" t="n">
+        <v>-1131</v>
+      </c>
+      <c r="R55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="16" t="n"/>
+      <c r="AA55" s="16" t="n"/>
+      <c r="AB55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" s="16" t="n"/>
+      <c r="AD55" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="16" t="n"/>
+      <c r="AF55" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG55" s="16" t="n"/>
+      <c r="AH55" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI55" s="16" t="n"/>
+      <c r="AJ55" s="16" t="n"/>
+      <c r="AK55" s="16" t="n"/>
+      <c r="AL55" s="16" t="n"/>
+      <c r="AM55" s="16" t="n"/>
+      <c r="AN55" s="16" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B56" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="inlineStr">
+        <is>
+          <t>'5213419655</t>
+        </is>
+      </c>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>'4634054712001</t>
+        </is>
+      </c>
+      <c r="E56" s="21" t="n">
+        <v>45897</v>
+      </c>
+      <c r="F56" s="16" t="inlineStr">
+        <is>
+          <t>'7701008101128</t>
+        </is>
+      </c>
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>Sao 112 San Felipe</t>
+        </is>
+      </c>
+      <c r="H56" s="16" t="inlineStr">
+        <is>
+          <t>'4634054712</t>
+        </is>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J56" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K56" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L56" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M56" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N56" s="16" t="n">
+        <v>-221909</v>
+      </c>
+      <c r="O56" s="16" t="n">
+        <v>-186478</v>
+      </c>
+      <c r="P56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" s="16" t="n">
+        <v>-35431</v>
+      </c>
+      <c r="R56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="16" t="n"/>
+      <c r="AA56" s="16" t="n"/>
+      <c r="AB56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC56" s="16" t="n"/>
+      <c r="AD56" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="16" t="n"/>
+      <c r="AF56" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG56" s="16" t="n"/>
+      <c r="AH56" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI56" s="16" t="n"/>
+      <c r="AJ56" s="16" t="n"/>
+      <c r="AK56" s="16" t="n"/>
+      <c r="AL56" s="16" t="n"/>
+      <c r="AM56" s="16" t="n"/>
+      <c r="AN56" s="16" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B57" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="inlineStr">
+        <is>
+          <t>'5313872796</t>
+        </is>
+      </c>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249400001</t>
+        </is>
+      </c>
+      <c r="E57" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F57" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H57" s="16" t="inlineStr">
+        <is>
+          <t>'4632027137</t>
+        </is>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J57" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K57" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L57" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M57" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N57" s="16" t="n">
+        <v>-220481</v>
+      </c>
+      <c r="O57" s="16" t="n">
+        <v>-185278</v>
+      </c>
+      <c r="P57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="16" t="n">
+        <v>-35203</v>
+      </c>
+      <c r="R57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="16" t="n"/>
+      <c r="AA57" s="16" t="n"/>
+      <c r="AB57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="16" t="n"/>
+      <c r="AD57" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="16" t="n"/>
+      <c r="AF57" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG57" s="16" t="n"/>
+      <c r="AH57" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI57" s="16" t="n"/>
+      <c r="AJ57" s="16" t="n"/>
+      <c r="AK57" s="16" t="n"/>
+      <c r="AL57" s="16" t="n"/>
+      <c r="AM57" s="16" t="n"/>
+      <c r="AN57" s="16" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B58" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="inlineStr">
+        <is>
+          <t>'5314056670</t>
+        </is>
+      </c>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249558001</t>
+        </is>
+      </c>
+      <c r="E58" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F58" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009608</t>
+        </is>
+      </c>
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>Bod 960 Cross-Docking</t>
+        </is>
+      </c>
+      <c r="H58" s="16" t="inlineStr">
+        <is>
+          <t>'4632109354</t>
+        </is>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J58" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K58" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L58" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M58" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N58" s="16" t="n">
+        <v>-96148</v>
+      </c>
+      <c r="O58" s="16" t="n">
+        <v>-80797</v>
+      </c>
+      <c r="P58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="16" t="n">
+        <v>-15351</v>
+      </c>
+      <c r="R58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="16" t="n"/>
+      <c r="AA58" s="16" t="n"/>
+      <c r="AB58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="16" t="n"/>
+      <c r="AD58" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="16" t="n"/>
+      <c r="AF58" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG58" s="16" t="n"/>
+      <c r="AH58" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI58" s="16" t="n"/>
+      <c r="AJ58" s="16" t="n"/>
+      <c r="AK58" s="16" t="n"/>
+      <c r="AL58" s="16" t="n"/>
+      <c r="AM58" s="16" t="n"/>
+      <c r="AN58" s="16" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B59" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C59" s="16" t="inlineStr">
+        <is>
+          <t>'5313592436</t>
+        </is>
+      </c>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249559001</t>
+        </is>
+      </c>
+      <c r="E59" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F59" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H59" s="16" t="inlineStr">
+        <is>
+          <t>'4632066563</t>
+        </is>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J59" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K59" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L59" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M59" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N59" s="16" t="n">
+        <v>-2395</v>
+      </c>
+      <c r="O59" s="16" t="n">
+        <v>-2013</v>
+      </c>
+      <c r="P59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="16" t="n">
+        <v>-382</v>
+      </c>
+      <c r="R59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="16" t="n"/>
+      <c r="AA59" s="16" t="n"/>
+      <c r="AB59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC59" s="16" t="n"/>
+      <c r="AD59" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="16" t="n"/>
+      <c r="AF59" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG59" s="16" t="n"/>
+      <c r="AH59" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI59" s="16" t="n"/>
+      <c r="AJ59" s="16" t="n"/>
+      <c r="AK59" s="16" t="n"/>
+      <c r="AL59" s="16" t="n"/>
+      <c r="AM59" s="16" t="n"/>
+      <c r="AN59" s="16" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B60" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C60" s="16" t="inlineStr">
+        <is>
+          <t>'5314087548</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249563001</t>
+        </is>
+      </c>
+      <c r="E60" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F60" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H60" s="16" t="inlineStr">
+        <is>
+          <t>'4632027134</t>
+        </is>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J60" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K60" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L60" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M60" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N60" s="16" t="n">
+        <v>-754</v>
+      </c>
+      <c r="O60" s="16" t="n">
+        <v>-634</v>
+      </c>
+      <c r="P60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="16" t="n">
+        <v>-120</v>
+      </c>
+      <c r="R60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="16" t="n"/>
+      <c r="AA60" s="16" t="n"/>
+      <c r="AB60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="16" t="n"/>
+      <c r="AD60" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="16" t="n"/>
+      <c r="AF60" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG60" s="16" t="n"/>
+      <c r="AH60" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI60" s="16" t="n"/>
+      <c r="AJ60" s="16" t="n"/>
+      <c r="AK60" s="16" t="n"/>
+      <c r="AL60" s="16" t="n"/>
+      <c r="AM60" s="16" t="n"/>
+      <c r="AN60" s="16" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B61" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C61" s="16" t="inlineStr">
+        <is>
+          <t>'5313928139</t>
+        </is>
+      </c>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249565001</t>
+        </is>
+      </c>
+      <c r="E61" s="21" t="n">
+        <v>45819</v>
+      </c>
+      <c r="F61" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009196</t>
+        </is>
+      </c>
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>Bodega 919 Cross Droking Bogotá</t>
+        </is>
+      </c>
+      <c r="H61" s="16" t="inlineStr">
+        <is>
+          <t>'4632027138</t>
+        </is>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J61" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K61" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L61" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M61" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N61" s="16" t="n">
+        <v>-634</v>
+      </c>
+      <c r="O61" s="16" t="n">
+        <v>-533</v>
+      </c>
+      <c r="P61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="16" t="n">
+        <v>-101</v>
+      </c>
+      <c r="R61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="16" t="n"/>
+      <c r="AA61" s="16" t="n"/>
+      <c r="AB61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC61" s="16" t="n"/>
+      <c r="AD61" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="16" t="n"/>
+      <c r="AF61" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG61" s="16" t="n"/>
+      <c r="AH61" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI61" s="16" t="n"/>
+      <c r="AJ61" s="16" t="n"/>
+      <c r="AK61" s="16" t="n"/>
+      <c r="AL61" s="16" t="n"/>
+      <c r="AM61" s="16" t="n"/>
+      <c r="AN61" s="16" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B62" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C62" s="16" t="inlineStr">
+        <is>
+          <t>'5314063653</t>
+        </is>
+      </c>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249972002</t>
+        </is>
+      </c>
+      <c r="E62" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F62" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H62" s="16" t="inlineStr">
+        <is>
+          <t>'4632066562</t>
+        </is>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J62" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K62" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L62" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M62" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N62" s="16" t="n">
+        <v>-289187</v>
+      </c>
+      <c r="O62" s="16" t="n">
+        <v>-243014</v>
+      </c>
+      <c r="P62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="16" t="n">
+        <v>-46173</v>
+      </c>
+      <c r="R62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="16" t="n"/>
+      <c r="AA62" s="16" t="n"/>
+      <c r="AB62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC62" s="16" t="n"/>
+      <c r="AD62" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="16" t="n"/>
+      <c r="AF62" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG62" s="16" t="n"/>
+      <c r="AH62" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI62" s="16" t="n"/>
+      <c r="AJ62" s="16" t="n"/>
+      <c r="AK62" s="16" t="n"/>
+      <c r="AL62" s="16" t="n"/>
+      <c r="AM62" s="16" t="n"/>
+      <c r="AN62" s="16" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B63" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C63" s="16" t="inlineStr">
+        <is>
+          <t>'5313978421</t>
+        </is>
+      </c>
+      <c r="D63" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1249976002</t>
+        </is>
+      </c>
+      <c r="E63" s="21" t="n">
+        <v>45820</v>
+      </c>
+      <c r="F63" s="16" t="inlineStr">
+        <is>
+          <t>'7701008109001</t>
+        </is>
+      </c>
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>Bod 900 Cross Doking Costa</t>
+        </is>
+      </c>
+      <c r="H63" s="16" t="inlineStr">
+        <is>
+          <t>'4632003303</t>
+        </is>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J63" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K63" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L63" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M63" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N63" s="16" t="n">
+        <v>-909</v>
+      </c>
+      <c r="O63" s="16" t="n">
+        <v>-764</v>
+      </c>
+      <c r="P63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="16" t="n">
+        <v>-145</v>
+      </c>
+      <c r="R63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="16" t="n"/>
+      <c r="AA63" s="16" t="n"/>
+      <c r="AB63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="16" t="n"/>
+      <c r="AD63" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="16" t="n"/>
+      <c r="AF63" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG63" s="16" t="n"/>
+      <c r="AH63" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI63" s="16" t="n"/>
+      <c r="AJ63" s="16" t="n"/>
+      <c r="AK63" s="16" t="n"/>
+      <c r="AL63" s="16" t="n"/>
+      <c r="AM63" s="16" t="n"/>
+      <c r="AN63" s="16" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C64" s="16" t="inlineStr">
+        <is>
+          <t>'5314002274</t>
+        </is>
+      </c>
+      <c r="D64" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250219002</t>
+        </is>
+      </c>
+      <c r="E64" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F64" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H64" s="16" t="inlineStr">
+        <is>
+          <t>'4632092530</t>
+        </is>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J64" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K64" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L64" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M64" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="n">
+        <v>-1597</v>
+      </c>
+      <c r="O64" s="16" t="n">
+        <v>-1342</v>
+      </c>
+      <c r="P64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="16" t="n">
+        <v>-255</v>
+      </c>
+      <c r="R64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="16" t="n"/>
+      <c r="AA64" s="16" t="n"/>
+      <c r="AB64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="16" t="n"/>
+      <c r="AD64" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="16" t="n"/>
+      <c r="AF64" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG64" s="16" t="n"/>
+      <c r="AH64" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI64" s="16" t="n"/>
+      <c r="AJ64" s="16" t="n"/>
+      <c r="AK64" s="16" t="n"/>
+      <c r="AL64" s="16" t="n"/>
+      <c r="AM64" s="16" t="n"/>
+      <c r="AN64" s="16" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="16" t="n">
+        <v>381</v>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>Nota Crédito</t>
+        </is>
+      </c>
+      <c r="C65" s="16" t="inlineStr">
+        <is>
+          <t>'5314088568</t>
+        </is>
+      </c>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>'PMP1250225002</t>
+        </is>
+      </c>
+      <c r="E65" s="21" t="n">
+        <v>45821</v>
+      </c>
+      <c r="F65" s="16" t="inlineStr">
+        <is>
+          <t>'7701008009455</t>
+        </is>
+      </c>
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>Bod 945 CEDI Cartagena</t>
+        </is>
+      </c>
+      <c r="H65" s="16" t="inlineStr">
+        <is>
+          <t>'4631938988</t>
+        </is>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="J65" s="16" t="inlineStr">
+        <is>
+          <t>'0</t>
+        </is>
+      </c>
+      <c r="K65" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="L65" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="M65" s="16" t="inlineStr">
+        <is>
+          <t>'</t>
+        </is>
+      </c>
+      <c r="N65" s="16" t="n">
+        <v>-368</v>
+      </c>
+      <c r="O65" s="16" t="n">
+        <v>-309</v>
+      </c>
+      <c r="P65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="16" t="n">
+        <v>-59</v>
+      </c>
+      <c r="R65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="16" t="n"/>
+      <c r="AA65" s="16" t="n"/>
+      <c r="AB65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="16" t="n"/>
+      <c r="AD65" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="16" t="n"/>
+      <c r="AF65" s="16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="AG65" s="16" t="n"/>
+      <c r="AH65" s="16" t="inlineStr">
+        <is>
+          <t>0.000</t>
+        </is>
+      </c>
+      <c r="AI65" s="16" t="n"/>
+      <c r="AJ65" s="16" t="n"/>
+      <c r="AK65" s="16" t="n"/>
+      <c r="AL65" s="16" t="n"/>
+      <c r="AM65" s="16" t="n"/>
+      <c r="AN65" s="16" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="15" t="inlineStr">
+        <is>
+          <t>Totales.</t>
+        </is>
+      </c>
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="n"/>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="n"/>
+      <c r="G66" s="16" t="n"/>
+      <c r="H66" s="16" t="n"/>
+      <c r="I66" s="16" t="n"/>
+      <c r="J66" s="16" t="n"/>
+      <c r="K66" s="16" t="n"/>
+      <c r="L66" s="16" t="n"/>
+      <c r="M66" s="16" t="n"/>
+      <c r="N66" s="16" t="n">
+        <v>1188745461</v>
+      </c>
+      <c r="O66" s="16" t="n">
+        <v>1000803412</v>
+      </c>
+      <c r="P66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="16" t="n">
+        <v>187942049</v>
+      </c>
+      <c r="R66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="16" t="n"/>
+      <c r="AA66" s="16" t="n"/>
+      <c r="AB66" s="16" t="n"/>
+      <c r="AC66" s="16" t="n"/>
+      <c r="AD66" s="16" t="n"/>
+      <c r="AE66" s="16" t="n"/>
+      <c r="AF66" s="16" t="n"/>
+      <c r="AG66" s="16" t="n"/>
+      <c r="AH66" s="16" t="n"/>
+      <c r="AI66" s="16" t="n"/>
+      <c r="AJ66" s="16" t="n"/>
+      <c r="AK66" s="16" t="n"/>
+      <c r="AL66" s="16" t="n"/>
+      <c r="AM66" s="16" t="n"/>
+      <c r="AN66" s="16" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/Archivos/Template/Template_HRC_olimpica.xlsx
+++ b/Archivos/Template/Template_HRC_olimpica.xlsx
@@ -601,7 +601,7 @@
         </is>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-141739081.6399999</v>
+        <v>141739081.6399999</v>
       </c>
     </row>
     <row r="9"/>
@@ -7722,6 +7722,19 @@
       <c r="AN66" s="16" t="n"/>
     </row>
   </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="D9:D14"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>